--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92026</v>
+        <v>92032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92032</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36908-2025 artfynd.xlsx
+++ b/artfynd/A 36908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533103</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128533101</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
